--- a/BE/StudentImportTemplate.xlsx
+++ b/BE/StudentImportTemplate.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="6072" yWindow="2328" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="5184" yWindow="972" windowWidth="17280" windowHeight="8964" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="99">
   <si>
     <t>StudentCode*</t>
   </si>
@@ -145,6 +145,9 @@
     <t>HeartRate</t>
   </si>
   <si>
+    <t>FALSE</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -154,7 +157,22 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>120/80</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>MMR, DTaP, Polio</t>
+  </si>
+  <si>
+    <t>All vaccinations up to date</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>No special notes</t>
   </si>
   <si>
     <t>Instructions for Excel Import</t>
@@ -253,49 +271,55 @@
     <t>29. For siblings with same parents, create separate parent records with same email but different relationships.</t>
   </si>
   <si>
-    <t>Nữ</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>STU1C026</t>
-  </si>
-  <si>
-    <t>Giang</t>
-  </si>
-  <si>
-    <t>Vũ Quỳnh</t>
-  </si>
-  <si>
-    <t>Khu tập thể Vietsopetro</t>
-  </si>
-  <si>
-    <t>1C</t>
-  </si>
-  <si>
-    <t>jZae72TK0BKAqmKSqQCdzwwXVqGrPKEglMjxcbJe</t>
-  </si>
-  <si>
-    <t>Vũ Mạnh</t>
-  </si>
-  <si>
-    <t>Cường</t>
-  </si>
-  <si>
-    <t>vumanhcuong@gmail.com</t>
-  </si>
-  <si>
-    <t>Oil and gas workers</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>True</t>
+    <t>jZae727K08KaOmKSgOaGzww/XVqGr/PKEgIMkjrcbJI=</t>
+  </si>
+  <si>
+    <t>Suyển</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>120/84</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>663 Hoàng Văn Thụ</t>
+  </si>
+  <si>
+    <t>Huyễn Hoa Linh (Mother)-3578694125</t>
+  </si>
+  <si>
+    <t>Lê</t>
+  </si>
+  <si>
+    <t>Công nhân</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t>STU0020</t>
+  </si>
+  <si>
+    <t>Can Minh</t>
+  </si>
+  <si>
+    <t>663 Hoàng Hoa Thám</t>
+  </si>
+  <si>
+    <t>Thảo Hiền</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>lethaohien@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -366,13 +390,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -382,14 +405,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -709,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.69921875" customWidth="1"/>
@@ -717,10 +736,9 @@
     <col min="3" max="3" width="12.19921875" customWidth="1"/>
     <col min="4" max="4" width="14.19921875" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.3984375" customWidth="1"/>
-    <col min="6" max="6" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.19921875" customWidth="1"/>
+    <col min="6" max="7" width="13.19921875" customWidth="1"/>
     <col min="8" max="8" width="13.796875" customWidth="1"/>
-    <col min="9" max="9" width="43.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -753,84 +771,44 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="3">
-        <v>43203</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="10">
+        <v>42819</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="I6" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" showErrorMessage="1" error="Please select Nam or Nữ for gender" sqref="E2:E1000">
+    <dataValidation type="list" showErrorMessage="1" error="Please select Nam or Nữ for gender" sqref="E2:E996">
       <formula1>"Nam,Nữ"</formula1>
     </dataValidation>
-    <dataValidation type="whole" showErrorMessage="1" error="Grade level must be between 1 and 5" sqref="H2:H1000">
+    <dataValidation type="whole" showErrorMessage="1" error="Grade level must be between 1 and 5" sqref="H2:H996">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThanOrEqual" showErrorMessage="1" error="Password must be at least 6 characters long" sqref="I2:I1000">
+    <dataValidation type="textLength" operator="greaterThanOrEqual" showErrorMessage="1" error="Password must be at least 6 characters long" sqref="I2:I996">
       <formula1>6</formula1>
     </dataValidation>
   </dataValidations>
@@ -840,7 +818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -848,11 +826,11 @@
     <col min="3" max="3" width="14.796875" customWidth="1"/>
     <col min="4" max="4" width="14.3984375" customWidth="1"/>
     <col min="5" max="5" width="21.3984375" customWidth="1"/>
-    <col min="6" max="6" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.19921875" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="22.09765625" customWidth="1"/>
     <col min="9" max="9" width="17.09765625" customWidth="1"/>
-    <col min="10" max="10" width="43.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -888,26 +866,26 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>77</v>
+      <c r="A2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="D2">
-        <v>1334567890</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" t="s">
-        <v>87</v>
+        <v>6741235890</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -915,57 +893,25 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="J6" s="10"/>
+      <c r="J2" s="9" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" showErrorMessage="1" error="Please select a valid relationship" sqref="C2:C1000">
+    <dataValidation type="list" showErrorMessage="1" error="Please select a valid relationship" sqref="C2:C996">
       <formula1>"Mother,Father,Guardian,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Please select TRUE or FALSE" sqref="H2:I1000">
+    <dataValidation type="list" showErrorMessage="1" error="Please select TRUE or FALSE" sqref="H2:I996">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="custom" showErrorMessage="1" error="Please enter a valid email address" sqref="E2:E1000">
+    <dataValidation type="custom" showErrorMessage="1" error="Please enter a valid email address" sqref="E2:E996">
       <formula1>ISNUMBER(MATCH("*@*.*",E2,0))</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThanOrEqual" showErrorMessage="1" error="Phone number must be at least 10 digits" sqref="D2:D1000">
+    <dataValidation type="textLength" operator="greaterThanOrEqual" showErrorMessage="1" error="Phone number must be at least 10 digits" sqref="D2:D996">
       <formula1>10</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThanOrEqual" showErrorMessage="1" error="Password must be at least 6 characters long" sqref="J2:J1000">
+    <dataValidation type="textLength" operator="greaterThanOrEqual" showErrorMessage="1" error="Password must be at least 6 characters long" sqref="J2:J996">
       <formula1>6</formula1>
     </dataValidation>
   </dataValidations>
@@ -978,7 +924,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.69921875" customWidth="1"/>
@@ -994,53 +940,26 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="10"/>
-      <c r="B3" s="13"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="13"/>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="13"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="10"/>
-      <c r="B6" s="13"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="10"/>
-      <c r="B7" s="13"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="10"/>
-      <c r="B8" s="13"/>
+      <c r="A2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" showErrorMessage="1" error="Please enter a valid email address" sqref="B2:B1002">
+    <dataValidation type="custom" showErrorMessage="1" error="Please enter a valid email address" sqref="B2:B996">
       <formula1>ISNUMBER(MATCH("*@*.*",B2,0))</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.69921875" customWidth="1"/>
@@ -1063,8 +982,8 @@
     <col min="18" max="18" width="24" customWidth="1"/>
     <col min="19" max="19" width="17.3984375" customWidth="1"/>
     <col min="20" max="21" width="9.09765625" customWidth="1"/>
-    <col min="22" max="22" width="32.69921875" style="6" customWidth="1"/>
-    <col min="23" max="23" width="16.69921875" style="6" customWidth="1"/>
+    <col min="22" max="22" width="32.69921875" style="5" customWidth="1"/>
+    <col min="23" max="23" width="16.69921875" style="5" customWidth="1"/>
     <col min="24" max="24" width="15.8984375" customWidth="1"/>
     <col min="25" max="25" width="11" customWidth="1"/>
   </cols>
@@ -1133,10 +1052,10 @@
       <c r="U1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="6" t="s">
         <v>37</v>
       </c>
       <c r="X1" s="1" t="s">
@@ -1147,125 +1066,96 @@
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="10" t="s">
-        <v>78</v>
+      <c r="A2" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>88</v>
+      <c r="E2" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
         <v>41</v>
       </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="T2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="10"/>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>130</v>
-      </c>
-      <c r="U2">
-        <v>20</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="W2" s="5"/>
+      <c r="W2" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="X2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" s="15">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="V3" s="16"/>
-      <c r="Y3" s="15"/>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="P4" s="10"/>
-      <c r="V4" s="16"/>
-      <c r="Y4" s="15"/>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="V5" s="16"/>
-      <c r="Y5" s="15"/>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="V6" s="16"/>
-      <c r="Y6" s="15"/>
+        <v>85</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" showErrorMessage="1" error="Please select a valid blood type" sqref="F2:F1000">
+    <dataValidation type="decimal" showErrorMessage="1" error="Height must be between 0 and 300 cm." sqref="T3:T996 U2">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" showErrorMessage="1" error="Weight must be between 0 and 500 kg." sqref="U3:U996">
+      <formula1>0</formula1>
+      <formula2>500</formula2>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" error="Please select a valid blood type" sqref="F2:F996">
       <formula1>"A+,A-,B+,B-,AB+,AB-,O+,O-"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Please select Yes, No, or Partial" sqref="O2:O1000">
+    <dataValidation type="list" showErrorMessage="1" error="Please select Yes, No, or Partial" sqref="O2:O996">
       <formula1>"Yes,No,Partial"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Please select TRUE or FALSE" sqref="R2:R1000 K2:K1000 G2:G1000 D2:D1000 B2:B1000">
+    <dataValidation type="list" showErrorMessage="1" error="Please select TRUE or FALSE" sqref="R2:R996 B2:B996 D2:D996 G2:G996 K2:K996">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="whole" showErrorMessage="1" error="Heart rate must be between 0 and 250 bpm." sqref="Y2:Y1000">
+    <dataValidation type="whole" showErrorMessage="1" error="Heart rate must be between 0 and 250 bpm." sqref="Y2:Y996">
       <formula1>0</formula1>
       <formula2>250</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" showErrorMessage="1" error="Height must be between 0 and 300 cm." sqref="T7:T1000 U2:U6">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" showErrorMessage="1" error="Weight must be between 0 and 500 kg." sqref="U7:U1000">
-      <formula1>0</formula1>
-      <formula2>500</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1281,171 +1171,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="87">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
     </row>
     <row r="3" spans="1:1" ht="41.4">
-      <c r="A3" s="9" t="s">
-        <v>45</v>
+      <c r="A3" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="179.4">
-      <c r="A4" s="9" t="s">
-        <v>46</v>
+      <c r="A4" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="55.2">
-      <c r="A5" s="9" t="s">
-        <v>47</v>
+      <c r="A5" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="138">
-      <c r="A6" s="9" t="s">
-        <v>48</v>
+      <c r="A6" s="8" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="179.4">
-      <c r="A7" s="9" t="s">
-        <v>49</v>
+      <c r="A7" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="138">
-      <c r="A8" s="9" t="s">
-        <v>50</v>
+      <c r="A8" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="69">
-      <c r="A9" s="9" t="s">
-        <v>51</v>
+      <c r="A9" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="69">
-      <c r="A10" s="9" t="s">
-        <v>52</v>
+      <c r="A10" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="110.4">
-      <c r="A11" s="9" t="s">
-        <v>53</v>
+      <c r="A11" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="69">
-      <c r="A12" s="9" t="s">
-        <v>54</v>
+      <c r="A12" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="69">
-      <c r="A13" s="9" t="s">
-        <v>55</v>
+      <c r="A13" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="110.4">
-      <c r="A14" s="9" t="s">
-        <v>56</v>
+      <c r="A14" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="82.8">
-      <c r="A15" s="9" t="s">
-        <v>57</v>
+      <c r="A15" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="82.8">
-      <c r="A16" s="9" t="s">
-        <v>58</v>
+      <c r="A16" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="110.4">
-      <c r="A17" s="9" t="s">
-        <v>59</v>
+      <c r="A17" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="96.6">
-      <c r="A18" s="9" t="s">
-        <v>60</v>
+      <c r="A18" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="151.80000000000001">
-      <c r="A19" s="9" t="s">
-        <v>61</v>
+      <c r="A19" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="179.4">
-      <c r="A20" s="9" t="s">
-        <v>62</v>
+      <c r="A20" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="124.2">
-      <c r="A21" s="9" t="s">
-        <v>63</v>
+      <c r="A21" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="96.6">
-      <c r="A22" s="9" t="s">
-        <v>64</v>
+      <c r="A22" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="82.8">
-      <c r="A23" s="9" t="s">
-        <v>65</v>
+      <c r="A23" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="82.8">
-      <c r="A24" s="9" t="s">
-        <v>66</v>
+      <c r="A24" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="138">
-      <c r="A25" s="9" t="s">
-        <v>67</v>
+      <c r="A25" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="9" t="s">
-        <v>40</v>
+      <c r="A26" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="69">
-      <c r="A27" s="9" t="s">
-        <v>68</v>
+      <c r="A27" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="96.6">
-      <c r="A28" s="9" t="s">
-        <v>69</v>
+      <c r="A28" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="124.2">
-      <c r="A29" s="9" t="s">
-        <v>70</v>
+      <c r="A29" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="138">
-      <c r="A30" s="9" t="s">
-        <v>71</v>
+      <c r="A30" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="124.2">
-      <c r="A31" s="9" t="s">
-        <v>72</v>
+      <c r="A31" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="138">
-      <c r="A32" s="9" t="s">
-        <v>73</v>
+      <c r="A32" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="151.80000000000001">
-      <c r="A33" s="9" t="s">
-        <v>74</v>
+      <c r="A33" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="179.4">
-      <c r="A34" s="9" t="s">
-        <v>75</v>
+      <c r="A34" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
